--- a/data/trans_dic/IP07_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68,57%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71,04%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>78,11%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>67,15%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>79,78%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69,02%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,2; 84,63</t>
+          <t>60,69; 75,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,42; 74,71</t>
+          <t>60,9; 77,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,38; 87,43</t>
+          <t>73,52; 89,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,86; 81,99</t>
+          <t>59,38; 80,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,07; 76,6</t>
+          <t>71,62; 84,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,49; 78,29</t>
+          <t>58,65; 74,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,52; 88,3</t>
+          <t>69,78; 86,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60,94; 81,5</t>
+          <t>62,22; 83,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,09; 78,8</t>
+          <t>67,95; 78,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,11; 74,51</t>
+          <t>62,29; 74,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74,81; 86,04</t>
+          <t>74,68; 85,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,73; 78,48</t>
+          <t>63,78; 79,39</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>76,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>76,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>88,53%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,32; 80,32</t>
+          <t>72,67; 78,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,7; 80,05</t>
+          <t>71,01; 77,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,7; 90,83</t>
+          <t>83,39; 88,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,07; 84,0</t>
+          <t>70,86; 79,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,94; 79,17</t>
+          <t>73,7; 80,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,29; 77,76</t>
+          <t>73,4; 79,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,43; 88,87</t>
+          <t>85,81; 90,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,16; 80,51</t>
+          <t>73,99; 80,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,16; 78,54</t>
+          <t>74,29; 78,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,42; 77,96</t>
+          <t>73,4; 78,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85,64; 89,1</t>
+          <t>85,58; 88,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,59; 80,75</t>
+          <t>74,07; 79,58</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>83,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86,26%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76,19%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>78,81%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>75,47%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>86,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73,73%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,08; 83,51</t>
+          <t>78,48; 88,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,23; 81,19</t>
+          <t>71,59; 82,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,52; 90,31</t>
+          <t>81,03; 89,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,3; 78,93</t>
+          <t>70,09; 81,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,89; 87,75</t>
+          <t>73,4; 83,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,28; 82,23</t>
+          <t>70,21; 80,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,16; 90,1</t>
+          <t>81,22; 89,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,67; 81,64</t>
+          <t>65,4; 78,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,2; 84,27</t>
+          <t>77,28; 84,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,28; 79,92</t>
+          <t>72,19; 80,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82,82; 89,08</t>
+          <t>82,91; 88,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,33; 78,99</t>
+          <t>70,15; 78,59</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>76,66%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,03; 80,03</t>
+          <t>74,07; 79,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,53; 77,8</t>
+          <t>72,27; 77,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 89,13</t>
+          <t>83,79; 88,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,08; 80,87</t>
+          <t>71,89; 78,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,15; 78,93</t>
+          <t>74,85; 79,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,98; 77,24</t>
+          <t>72,36; 78,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,01</t>
+          <t>85,05; 89,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,76; 78,85</t>
+          <t>73,32; 79,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75,26; 78,92</t>
+          <t>75,31; 78,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,9; 76,84</t>
+          <t>73,08; 76,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85,09; 87,93</t>
+          <t>85,07; 87,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,06; 78,96</t>
+          <t>73,74; 78,13</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60035</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56261</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40304</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>70972</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>62028</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>47370</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37736</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>59107</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60035</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56261</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44810</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82546</t>
+          <t>75070</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64694; 76900</t>
+          <t>52316; 65391</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53966; 69012</t>
+          <t>51983; 66505</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41789; 51916</t>
+          <t>50448; 61200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24530; 44832</t>
+          <t>33686; 45659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51785; 66031</t>
+          <t>65082; 77192</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52480; 66823</t>
+          <t>54172; 69176</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49756; 60583</t>
+          <t>41434; 51584</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37785; 50535</t>
+          <t>29092; 39227</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120559; 139526</t>
+          <t>120321; 139407</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112154; 132428</t>
+          <t>110702; 131603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95748; 110123</t>
+          <t>95590; 109897</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68523; 91572</t>
+          <t>66001; 82157</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>482</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>501</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>360728</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>366677</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>419993</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>362106</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>320312</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>346309</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>415190</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>365430</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>360728</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>366677</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>419993</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>395706</t>
+          <t>336570</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>761136</t>
+          <t>698676</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>305056; 334188</t>
+          <t>345525; 375432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>332209; 360836</t>
+          <t>349124; 381948</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>401937; 425981</t>
+          <t>405737; 430620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>350333; 386810</t>
+          <t>337053; 379476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>346825; 376458</t>
+          <t>306644; 333633</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>350500; 382269</t>
+          <t>330851; 359755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>405941; 432412</t>
+          <t>402426; 426428</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>367617; 415917</t>
+          <t>319950; 350058</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>661174; 700255</t>
+          <t>662312; 700725</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>691876; 734734</t>
+          <t>691701; 735344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>818307; 851401</t>
+          <t>817767; 849982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>728880; 789062</t>
+          <t>672623; 722687</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131462</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132963</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>161182</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128310</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>137187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>125302</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>147567</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110263</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>131462</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>132963</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>161182</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>139163</t>
+          <t>109412</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>249426</t>
+          <t>237723</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>127200; 145363</t>
+          <t>123576; 138751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>114943; 134796</t>
+          <t>123305; 142597</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139731; 154799</t>
+          <t>151403; 167775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100655; 118037</t>
+          <t>118046; 137547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>122653; 138184</t>
+          <t>127760; 145060</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>122770; 141618</t>
+          <t>116571; 133653</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>151645; 168344</t>
+          <t>139220; 154164</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>127742; 149688</t>
+          <t>98086; 117395</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>255949; 279397</t>
+          <t>256214; 279184</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>244482; 270330</t>
+          <t>244196; 271429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>296702; 319133</t>
+          <t>297033; 318483</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>234124; 262946</t>
+          <t>223356; 250224</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>711</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>551297</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>559675</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>513428</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>551297</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>559675</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>480748</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1093107</t>
+          <t>1011468</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>510969; 544993</t>
+          <t>532649; 568756</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>514352; 551741</t>
+          <t>541469; 580497</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>592800; 623724</t>
+          <t>621765; 653037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>492434; 537569</t>
+          <t>503826; 550622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>533273; 567664</t>
+          <t>509734; 544114</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>539273; 578663</t>
+          <t>513145; 553843</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>620838; 653042</t>
+          <t>595178; 622956</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>546755; 600807</t>
+          <t>461293; 497384</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1053815; 1105065</t>
+          <t>1054462; 1105437</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1063126; 1120640</t>
+          <t>1065822; 1120904</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1226851; 1267830</t>
+          <t>1226504; 1268462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1056670; 1126520</t>
+          <t>980729; 1039151</t>
         </is>
       </c>
     </row>
